--- a/data/trans_camb/IP16A01-Dificultad-trans_camb.xlsx
+++ b/data/trans_camb/IP16A01-Dificultad-trans_camb.xlsx
@@ -40,7 +40,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -66,13 +66,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border>
@@ -513,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:H34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -524,9 +517,6 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,68 +532,50 @@
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
-      <c r="E1" s="3" t="n"/>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>Niña</t>
         </is>
       </c>
-      <c r="G1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="H1" s="3" t="n"/>
-      <c r="I1" s="3" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="J1" s="3" t="n"/>
-      <c r="K1" s="3" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="4" t="n"/>
       <c r="B2" s="2" t="n"/>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="D2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="F2" s="3" t="inlineStr">
         <is>
-          <t>2012/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
       <c r="G2" s="3" t="inlineStr">
         <is>
-          <t>2016/2007</t>
+          <t>2016/2012</t>
         </is>
       </c>
       <c r="H2" s="3" t="inlineStr">
         <is>
-          <t>2023/2007</t>
-        </is>
-      </c>
-      <c r="I2" s="3" t="inlineStr">
-        <is>
-          <t>2012/2007</t>
-        </is>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>2016/2007</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>2023/2007</t>
+          <t>2023/2012</t>
         </is>
       </c>
     </row>
@@ -616,9 +588,6 @@
       <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="n"/>
       <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="n"/>
-      <c r="J3" s="2" t="n"/>
-      <c r="K3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -631,15 +600,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr"/>
-      <c r="D4" s="5" t="inlineStr"/>
-      <c r="E4" s="5" t="inlineStr"/>
-      <c r="F4" s="5" t="inlineStr"/>
-      <c r="G4" s="5" t="inlineStr"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="5" t="inlineStr"/>
-      <c r="J4" s="5" t="inlineStr"/>
-      <c r="K4" s="5" t="inlineStr"/>
+      <c r="C4" s="5" t="n">
+        <v>-5.542935233332684</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-2.053018471883661</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-1.269450039688194</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.359789611091537</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>-3.508995546685047</v>
+      </c>
+      <c r="H4" s="5" t="n">
+        <v>-3.58728779421872</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
@@ -648,15 +626,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr"/>
-      <c r="D5" s="5" t="inlineStr"/>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="5" t="inlineStr"/>
+      <c r="C5" s="5" t="n">
+        <v>-9.923538350770999</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-8.538809930882879</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.386206419990812</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-12.08472172076501</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>-7.185424643765312</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>-8.201508046610597</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n"/>
@@ -665,15 +652,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr"/>
-      <c r="D6" s="5" t="inlineStr"/>
-      <c r="E6" s="5" t="inlineStr"/>
-      <c r="F6" s="5" t="inlineStr"/>
-      <c r="G6" s="5" t="inlineStr"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="5" t="inlineStr"/>
-      <c r="J6" s="5" t="inlineStr"/>
-      <c r="K6" s="5" t="inlineStr"/>
+      <c r="C6" s="5" t="n">
+        <v>-0.9314724250495846</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>5.035943296453156</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.839308791734228</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.790814697864416</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.1780697849448139</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>2.833097456943479</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n"/>
@@ -682,15 +678,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr"/>
-      <c r="D7" s="6" t="inlineStr"/>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="inlineStr"/>
-      <c r="I7" s="6" t="inlineStr"/>
-      <c r="J7" s="6" t="inlineStr"/>
-      <c r="K7" s="6" t="inlineStr"/>
+      <c r="C7" s="6" t="n">
+        <v>-0.3618469351979232</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>-0.1340225730022054</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>-0.08331375686947438</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>-0.3517619398709825</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.2296649010928673</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2347891541866469</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n"/>
@@ -699,15 +704,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr"/>
-      <c r="D8" s="6" t="inlineStr"/>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr"/>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="inlineStr"/>
-      <c r="I8" s="6" t="inlineStr"/>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr"/>
+      <c r="C8" s="6" t="n">
+        <v>-0.5565731145378372</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-0.501236226053315</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-0.3634382589605109</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>-0.7299226660454332</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.414047068534957</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.4939225691130227</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
@@ -716,15 +730,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr"/>
-      <c r="D9" s="6" t="inlineStr"/>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="inlineStr"/>
-      <c r="I9" s="6" t="inlineStr"/>
-      <c r="J9" s="6" t="inlineStr"/>
-      <c r="K9" s="6" t="inlineStr"/>
+      <c r="C9" s="6" t="n">
+        <v>-0.06484857220263497</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>0.4071392856634642</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>0.3166660931522886</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>0.390042725190714</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.01582446661296082</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.1967248789992447</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -737,15 +760,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr"/>
-      <c r="D10" s="5" t="inlineStr"/>
-      <c r="E10" s="5" t="inlineStr"/>
-      <c r="F10" s="5" t="inlineStr"/>
-      <c r="G10" s="5" t="inlineStr"/>
-      <c r="H10" s="5" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="n">
+        <v>-2.813171184443007</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>-1.17029374467074</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9249622992915485</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.1753248035887917</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>-1.874095682033793</v>
+      </c>
+      <c r="H10" s="5" t="n">
+        <v>-0.7301005726468163</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
@@ -754,15 +786,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr"/>
-      <c r="D11" s="5" t="inlineStr"/>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
-      <c r="H11" s="5" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
-      <c r="K11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="n">
+        <v>-7.835815578508767</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-6.714747776878364</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-6.374420160079955</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.614673272091332</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>-5.269318758525598</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>-4.745567614615179</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n"/>
@@ -771,15 +812,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr"/>
-      <c r="D12" s="5" t="inlineStr"/>
-      <c r="E12" s="5" t="inlineStr"/>
-      <c r="F12" s="5" t="inlineStr"/>
-      <c r="G12" s="5" t="inlineStr"/>
-      <c r="H12" s="5" t="inlineStr"/>
-      <c r="I12" s="5" t="inlineStr"/>
-      <c r="J12" s="5" t="inlineStr"/>
-      <c r="K12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="n">
+        <v>2.133524161684203</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>4.034643942581915</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>4.147690881878336</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>4.526229442419988</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>1.782197782023924</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>2.928508465313962</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n"/>
@@ -788,15 +838,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr"/>
-      <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="inlineStr"/>
-      <c r="I13" s="6" t="inlineStr"/>
-      <c r="J13" s="6" t="inlineStr"/>
-      <c r="K13" s="6" t="inlineStr"/>
+      <c r="C13" s="6" t="n">
+        <v>-0.2327754130183674</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>-0.09683577425896327</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>-0.07081570491160202</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>-0.01342297903832187</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.149040556556211</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.05806245472547213</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n"/>
@@ -805,15 +864,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="inlineStr"/>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr"/>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="inlineStr"/>
-      <c r="I14" s="6" t="inlineStr"/>
-      <c r="J14" s="6" t="inlineStr"/>
-      <c r="K14" s="6" t="inlineStr"/>
+      <c r="C14" s="6" t="n">
+        <v>-0.5280583338220477</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>-0.4501298665905951</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>-0.4038163655477531</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>-0.3689414514856618</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.3716475568520128</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3225275470982484</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
@@ -822,15 +890,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr"/>
-      <c r="D15" s="6" t="inlineStr"/>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr"/>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="inlineStr"/>
-      <c r="I15" s="6" t="inlineStr"/>
-      <c r="J15" s="6" t="inlineStr"/>
-      <c r="K15" s="6" t="inlineStr"/>
+      <c r="C15" s="6" t="n">
+        <v>0.214617046216704</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>0.4438128239087625</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>0.4030046719158907</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>0.4410668670024531</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1700634001942499</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2667946967539253</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -843,15 +920,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr"/>
-      <c r="D16" s="5" t="inlineStr"/>
-      <c r="E16" s="5" t="inlineStr"/>
-      <c r="F16" s="5" t="inlineStr"/>
-      <c r="G16" s="5" t="inlineStr"/>
-      <c r="H16" s="5" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
-      <c r="K16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="n">
+        <v>-5.877882639851742</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>3.801286285630456</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-6.83717921455038</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.3994934123259672</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-6.373284239514408</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>1.920933312354395</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
@@ -860,15 +946,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr"/>
-      <c r="D17" s="5" t="inlineStr"/>
-      <c r="E17" s="5" t="inlineStr"/>
-      <c r="F17" s="5" t="inlineStr"/>
-      <c r="G17" s="5" t="inlineStr"/>
-      <c r="H17" s="5" t="inlineStr"/>
-      <c r="I17" s="5" t="inlineStr"/>
-      <c r="J17" s="5" t="inlineStr"/>
-      <c r="K17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="n">
+        <v>-11.74702755024424</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-2.111801236326888</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-12.56458094361013</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-6.582541624593779</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>-10.24398487588948</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-2.863200705392826</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n"/>
@@ -877,15 +972,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr"/>
-      <c r="D18" s="5" t="inlineStr"/>
-      <c r="E18" s="5" t="inlineStr"/>
-      <c r="F18" s="5" t="inlineStr"/>
-      <c r="G18" s="5" t="inlineStr"/>
-      <c r="H18" s="5" t="inlineStr"/>
-      <c r="I18" s="5" t="inlineStr"/>
-      <c r="J18" s="5" t="inlineStr"/>
-      <c r="K18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="n">
+        <v>-0.262435347174795</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>9.922698316429237</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>-1.676050051961143</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>5.066129898758493</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>-2.462636192522547</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>5.858786896613259</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n"/>
@@ -894,15 +998,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr"/>
-      <c r="D19" s="6" t="inlineStr"/>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr"/>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="inlineStr"/>
-      <c r="I19" s="6" t="inlineStr"/>
-      <c r="J19" s="6" t="inlineStr"/>
-      <c r="K19" s="6" t="inlineStr"/>
+      <c r="C19" s="6" t="n">
+        <v>-0.4489272097411195</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.2903257771880774</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>-0.5347906400798406</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>-0.03124758485645944</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>-0.4924709337709327</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>0.1484327054145222</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n"/>
@@ -911,15 +1024,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr"/>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr"/>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="inlineStr"/>
-      <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr"/>
-      <c r="K20" s="6" t="inlineStr"/>
+      <c r="C20" s="6" t="n">
+        <v>-0.703332802646935</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-0.1331790556045333</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-0.7715046893860391</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-0.4238497164989555</v>
+      </c>
+      <c r="G20" s="6" t="n">
+        <v>-0.6779539189725955</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>-0.1833701707359078</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n"/>
@@ -928,15 +1050,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr"/>
-      <c r="D21" s="6" t="inlineStr"/>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr"/>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="inlineStr"/>
-      <c r="I21" s="6" t="inlineStr"/>
-      <c r="J21" s="6" t="inlineStr"/>
-      <c r="K21" s="6" t="inlineStr"/>
+      <c r="C21" s="6" t="n">
+        <v>0.01136892221821374</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>1.018684702928918</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>-0.1383231633263012</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>0.5395086866860294</v>
+      </c>
+      <c r="G21" s="6" t="n">
+        <v>-0.2173785923059873</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>0.58354899701253</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -949,15 +1080,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr"/>
-      <c r="D22" s="5" t="inlineStr"/>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr"/>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="5" t="inlineStr"/>
-      <c r="J22" s="5" t="inlineStr"/>
-      <c r="K22" s="5" t="inlineStr"/>
+      <c r="C22" s="5" t="n">
+        <v>-0.9831770875527348</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>3.363407824075637</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-6.800698909476774</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-2.667997081983162</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>-3.59168071482192</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.5713289531934507</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n"/>
@@ -966,15 +1106,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr"/>
-      <c r="D23" s="5" t="inlineStr"/>
-      <c r="E23" s="5" t="inlineStr"/>
-      <c r="F23" s="5" t="inlineStr"/>
-      <c r="G23" s="5" t="inlineStr"/>
-      <c r="H23" s="5" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
-      <c r="J23" s="5" t="inlineStr"/>
-      <c r="K23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="n">
+        <v>-7.929135828227454</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-4.046359418504059</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-16.22295575802291</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-11.91002610243791</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>-9.51328932851229</v>
+      </c>
+      <c r="H23" s="5" t="n">
+        <v>-5.078123657165104</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n"/>
@@ -983,15 +1132,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr"/>
-      <c r="D24" s="5" t="inlineStr"/>
-      <c r="E24" s="5" t="inlineStr"/>
-      <c r="F24" s="5" t="inlineStr"/>
-      <c r="G24" s="5" t="inlineStr"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
-      <c r="J24" s="5" t="inlineStr"/>
-      <c r="K24" s="5" t="inlineStr"/>
+      <c r="C24" s="5" t="n">
+        <v>5.866493201964857</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>11.27476275030007</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1.608124129389472</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>5.119869242189282</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>1.779362103245175</v>
+      </c>
+      <c r="H24" s="5" t="n">
+        <v>5.398011084894645</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n"/>
@@ -1000,15 +1158,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="6" t="inlineStr"/>
-      <c r="E25" s="6" t="inlineStr"/>
-      <c r="F25" s="6" t="inlineStr"/>
-      <c r="G25" s="6" t="inlineStr"/>
-      <c r="H25" s="6" t="inlineStr"/>
-      <c r="I25" s="6" t="inlineStr"/>
-      <c r="J25" s="6" t="inlineStr"/>
-      <c r="K25" s="6" t="inlineStr"/>
+      <c r="C25" s="6" t="n">
+        <v>-0.08665367014140535</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>0.2964385926282477</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-0.4334793258214032</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>-0.1700592235865521</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>-0.26990246208116</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>0.04293340732900022</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n"/>
@@ -1017,15 +1184,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr"/>
-      <c r="D26" s="6" t="inlineStr"/>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr"/>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6" t="inlineStr"/>
-      <c r="I26" s="6" t="inlineStr"/>
-      <c r="J26" s="6" t="inlineStr"/>
-      <c r="K26" s="6" t="inlineStr"/>
+      <c r="C26" s="6" t="n">
+        <v>-0.5392940274646545</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>-0.2782797191969923</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>-0.744678904434439</v>
+      </c>
+      <c r="F26" s="6" t="n">
+        <v>-0.5456824809335844</v>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>-0.5613140816269662</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>-0.3034300469481843</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n"/>
@@ -1034,15 +1210,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr"/>
-      <c r="D27" s="6" t="inlineStr"/>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr"/>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6" t="inlineStr"/>
-      <c r="I27" s="6" t="inlineStr"/>
-      <c r="J27" s="6" t="inlineStr"/>
-      <c r="K27" s="6" t="inlineStr"/>
+      <c r="C27" s="6" t="n">
+        <v>0.8192342433230755</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>1.631143957667281</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>0.2142638795663949</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>0.4870768998803488</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>0.1546171459485025</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>0.5238087089427491</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -1055,15 +1240,24 @@
           <t>Cambio absoluto (puntos porcentuales)</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr"/>
-      <c r="D28" s="5" t="inlineStr"/>
-      <c r="E28" s="5" t="inlineStr"/>
-      <c r="F28" s="5" t="inlineStr"/>
-      <c r="G28" s="5" t="inlineStr"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="n">
+        <v>-4.129152951394173</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.7457222782231487</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>-2.981823884075294</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-1.716980187437132</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>-3.575319517859318</v>
+      </c>
+      <c r="H28" s="5" t="n">
+        <v>-0.4217868781050182</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n"/>
@@ -1072,15 +1266,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr"/>
-      <c r="D29" s="5" t="inlineStr"/>
-      <c r="E29" s="5" t="inlineStr"/>
-      <c r="F29" s="5" t="inlineStr"/>
-      <c r="G29" s="5" t="inlineStr"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
-      <c r="K29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="n">
+        <v>-6.689759064784578</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>-2.693142997632649</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>-5.793233378994122</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-4.846774547021474</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>-5.4306354257686</v>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>-2.651549353721411</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n"/>
@@ -1089,15 +1292,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr"/>
-      <c r="D30" s="5" t="inlineStr"/>
-      <c r="E30" s="5" t="inlineStr"/>
-      <c r="F30" s="5" t="inlineStr"/>
-      <c r="G30" s="5" t="inlineStr"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
-      <c r="K30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="n">
+        <v>-1.45041612403058</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>3.768633586261096</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>-0.07709284010514988</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>1.494434571380363</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>-1.617761321862934</v>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>1.83558844383553</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n"/>
@@ -1106,15 +1318,24 @@
           <t>Cambio relativo (%)</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="6" t="inlineStr"/>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr"/>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6" t="inlineStr"/>
-      <c r="I31" s="6" t="inlineStr"/>
-      <c r="J31" s="6" t="inlineStr"/>
-      <c r="K31" s="6" t="inlineStr"/>
+      <c r="C31" s="6" t="n">
+        <v>-0.3096921191972932</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.05593019086337891</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>-0.2121612915597375</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-0.1221657442931475</v>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>-0.2612537838836168</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>-0.03082057906907602</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n"/>
@@ -1123,15 +1344,24 @@
           <t>IC 95% inferior</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr"/>
-      <c r="D32" s="6" t="inlineStr"/>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr"/>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6" t="inlineStr"/>
-      <c r="I32" s="6" t="inlineStr"/>
-      <c r="J32" s="6" t="inlineStr"/>
-      <c r="K32" s="6" t="inlineStr"/>
+      <c r="C32" s="6" t="n">
+        <v>-0.4548865065832253</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>-0.1749333448951118</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-0.3857931241778909</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-0.3115917464724479</v>
+      </c>
+      <c r="G32" s="6" t="n">
+        <v>-0.3743463111338541</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>-0.1822374541281819</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n"/>
@@ -1140,15 +1370,24 @@
           <t>IC 95% superior</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr"/>
-      <c r="D33" s="6" t="inlineStr"/>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr"/>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6" t="inlineStr"/>
-      <c r="I33" s="6" t="inlineStr"/>
-      <c r="J33" s="6" t="inlineStr"/>
-      <c r="K33" s="6" t="inlineStr"/>
+      <c r="C33" s="6" t="n">
+        <v>-0.1166849646334891</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>0.3142350935670006</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-0.007464117653635879</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0.1192940165426573</v>
+      </c>
+      <c r="G33" s="6" t="n">
+        <v>-0.1312795798808216</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>0.1444334483191877</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1159,11 +1398,11 @@
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A22:A27"/>
     <mergeCell ref="A4:A9"/>
-    <mergeCell ref="F1:H1"/>
-    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="E1:F1"/>
     <mergeCell ref="A16:A21"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A28:A33"/>
